--- a/out/LSTM_Base_repeat_2_000001.xlsx
+++ b/out/LSTM_Base_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.017459022789986</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.017459022789986</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.017459022789986</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003476286267624236</v>
+        <v>-5.756669758725911e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1496786865894358</v>
+        <v>0.02478644151927139</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2997570409904923</v>
+        <v>0.04963924646850443</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5782887517338183</v>
+        <v>0.0957639593566835</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.307038410988832</v>
+        <v>0.2164438953364906</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1778843527415734</v>
+        <v>0.02945753072326762</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.0837873191396</v>
+        <v>0.179473768334904</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03609426495503422</v>
+        <v>0.00597610995085539</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9778121935980986</v>
+        <v>0.1619234161748735</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0312592375844045</v>
+        <v>0.005174115645872323</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.004196501116446</v>
+        <v>0.1662902512581174</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01528193181570523</v>
+        <v>0.002526964121082358</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.003460805572247</v>
+        <v>0.166164722101992</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007292102164901733</v>
+        <v>0.001203054272881818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.002744094057197</v>
+        <v>0.1660418645222371</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003034637708602061</v>
+        <v>0.0004982660235487662</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.001513446946305</v>
+        <v>0.1658338437499779</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002101663167771313</v>
+        <v>0.0003437955134918071</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.002679598554854</v>
+        <v>0.1660229282910768</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008744517873018686</v>
+        <v>0.0001406088673481482</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.002324421339513</v>
+        <v>0.1659598438105695</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004513612103862177</v>
+        <v>7.050339205511362e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.002351130463586</v>
+        <v>0.1659601138893289</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001739786534795293</v>
+        <v>2.491725292766325e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.002247715029825</v>
+        <v>0.1659386871990606</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2920287688437e-05</v>
+        <v>1.103373131740489e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.002258851888344</v>
+        <v>0.1659363773182503</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.299709723600378e-05</v>
+        <v>2.905404250635916e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.002252380373355</v>
+        <v>0.1659311282928672</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.791150147070719e-05</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.002244585095189</v>
+        <v>0.1659256413632066</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.002236476097498</v>
+        <v>0.1659200628379036</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.002230411876459</v>
+        <v>0.1659148693431695</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.002224354794741</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.002218539292588</v>
+        <v>0.1659095415488468</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.002213657994339</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.002208736792791</v>
+        <v>0.1659096212597913</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.002208728821696</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.002208888243585</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.002209143318608</v>
+        <v>0.1659100277856088</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.00220889621468</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.002208856359208</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.002208864330302</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.00220889621468</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.002208991867813</v>
+        <v>0.1659098763348141</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.002208928099058</v>
+        <v>0.1659098125660582</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.002208888243585</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.002208864330302</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.002208617226374</v>
+        <v>0.1659095016933745</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.002208537515429</v>
+        <v>0.1659094219824297</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.002208585341996</v>
+        <v>0.1659094698089964</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.002208704908413</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.002208688966224</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.002208704908413</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.002208688966224</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.002208744763885</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.002208744763885</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.002208744763885</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.00220889621468</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.00220911143423</v>
+        <v>0.165909995901231</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.002209023752191</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.002208975925625</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.002209023752191</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.002208840417019</v>
+        <v>0.1659097248840192</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.002208848388113</v>
+        <v>0.1659097328551137</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.002208856359208</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.002208864330302</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.002208864330302</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.002208904185774</v>
+        <v>0.1659097886527749</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.00220896795453</v>
+        <v>0.1659098524215308</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.03186320216187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.002209079549853</v>
+        <v>0.1659099640168531</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.002209127376419</v>
+        <v>0.1659100118434199</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.002209087520947</v>
+        <v>0.1659099719879476</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.002209015781097</v>
+        <v>0.1659099002480975</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.002209135347514</v>
+        <v>0.1659100198145143</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.002208975925625</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.002208744763885</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.002208696937319</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.002208728821696</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.002208712879507</v>
+        <v>0.165909597346508</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.00220859331309</v>
+        <v>0.1659094777800909</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.002208553457618</v>
+        <v>0.1659094379246186</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.002208696937319</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.002208832445924</v>
+        <v>0.1659097169129248</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.002208816503735</v>
+        <v>0.1659097009707359</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.00220875273498</v>
+        <v>0.1659096372019802</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.002208649110752</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.002208529544335</v>
+        <v>0.1659094140113352</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.002208649110752</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.002208696937319</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.002208792590452</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.002208673024035</v>
+        <v>0.1659095574910357</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.00220868099513</v>
+        <v>0.1659095654621301</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000001.xlsx
+++ b/out/LSTM_Base_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187196</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187198</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003476286267624236</v>
+        <v>-0.0002660688213552349</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1496786865894358</v>
+        <v>0.1145614023813524</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2997570409904923</v>
+        <v>0.2294287538274813</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5782887517338183</v>
+        <v>0.4426121109477181</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.307038410988832</v>
+        <v>1.000384322575063</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1778843527415734</v>
+        <v>0.1361494574716301</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.0837873191396</v>
+        <v>0.829511836150113</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03609426495503422</v>
+        <v>0.02762594425353835</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187198</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9778121935980986</v>
+        <v>0.7484002547363208</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0312592375844045</v>
+        <v>0.02392529550028762</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.004196501116446</v>
+        <v>0.7685943606303764</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01528193181570523</v>
+        <v>0.01169618414811576</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.003460805572247</v>
+        <v>0.7680312725147437</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007292102164901733</v>
+        <v>0.005580246497245086</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.002744094057197</v>
+        <v>0.7674815241808638</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003034637708602061</v>
+        <v>0.002321491938506962</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.001513446946305</v>
+        <v>0.7665384065563169</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002101663167771313</v>
+        <v>0.001607793414154595</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.002679598554854</v>
+        <v>0.7674298377112646</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008744517873018686</v>
+        <v>0.0006682799397292695</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.002324421339513</v>
+        <v>0.767156850961571</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004513612103862177</v>
+        <v>0.0003437855809979584</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.002351130463586</v>
+        <v>0.76717610937378</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001739786534795293</v>
+        <v>0.0001319895265635107</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.002247715029825</v>
+        <v>0.7670957489439035</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2920287688437e-05</v>
+        <v>7.001495723500145e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.002258851888344</v>
+        <v>0.7671031110986752</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.299709723600378e-05</v>
+        <v>3.170366259223818e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.002252380373355</v>
+        <v>0.7670969839469558</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.791150147070719e-05</v>
+        <v>1.258324531472877e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.002244585095189</v>
+        <v>0.7670898387334796</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.002236476097498</v>
+        <v>0.7670824528924171</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.002230411876459</v>
+        <v>0.7670766310869136</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.002224354794741</v>
+        <v>0.7670707662909124</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.002218539292588</v>
+        <v>0.7670650871142042</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.002213657994339</v>
+        <v>0.7670602058159548</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.002208736792791</v>
+        <v>0.767055284614407</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.002208728821696</v>
+        <v>0.7670552766433125</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.002208888243585</v>
+        <v>0.7670554360652017</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.002209143318608</v>
+        <v>0.7670556911402244</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.00220889621468</v>
+        <v>0.7670554440362961</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.002208856359208</v>
+        <v>0.7670554041808239</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.002208864330302</v>
+        <v>0.7670554121519183</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187196</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.00220889621468</v>
+        <v>0.7670554440362961</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.002208991867813</v>
+        <v>0.7670555396894299</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.002208928099058</v>
+        <v>0.7670554759206739</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.002208888243585</v>
+        <v>0.7670554360652017</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.002208864330302</v>
+        <v>0.7670554121519183</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.002208617226374</v>
+        <v>0.7670551650479902</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.002208537515429</v>
+        <v>0.7670550853370454</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.002208585341996</v>
+        <v>0.7670551331636121</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.002208704908413</v>
+        <v>0.7670552527300292</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.002208688966224</v>
+        <v>0.7670552367878403</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.002208704908413</v>
+        <v>0.7670552527300292</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.002208688966224</v>
+        <v>0.7670552367878403</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.002208744763885</v>
+        <v>0.7670552925855014</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.002208744763885</v>
+        <v>0.7670552925855014</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.002208744763885</v>
+        <v>0.7670552925855014</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.00220889621468</v>
+        <v>0.7670554440362961</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.00220911143423</v>
+        <v>0.7670556592558466</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.002209023752191</v>
+        <v>0.7670555715738077</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.002208975925625</v>
+        <v>0.7670555237472408</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.002209023752191</v>
+        <v>0.7670555715738077</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.002208840417019</v>
+        <v>0.7670553882386349</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.002208848388113</v>
+        <v>0.7670553962097294</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.002208856359208</v>
+        <v>0.7670554041808239</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.002208864330302</v>
+        <v>0.7670554121519183</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187196</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.002208864330302</v>
+        <v>0.7670554121519183</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.002208904185774</v>
+        <v>0.7670554520073906</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.00220896795453</v>
+        <v>0.7670555157761464</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.002209079549853</v>
+        <v>0.7670556273714688</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.002209127376419</v>
+        <v>0.7670556751980355</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.002209087520947</v>
+        <v>0.7670556353425633</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.002209015781097</v>
+        <v>0.7670555636027132</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.002209135347514</v>
+        <v>0.76705568316913</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.002208975925625</v>
+        <v>0.7670555237472408</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.002208744763885</v>
+        <v>0.7670552925855014</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.002208696937319</v>
+        <v>0.7670552447589347</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.002208728821696</v>
+        <v>0.7670552766433125</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.002208712879507</v>
+        <v>0.7670552607011236</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.00220859331309</v>
+        <v>0.7670551411347065</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.002208553457618</v>
+        <v>0.7670551012792343</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.002208696937319</v>
+        <v>0.7670552447589347</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.002208832445924</v>
+        <v>0.7670553802675405</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.002208816503735</v>
+        <v>0.7670553643253516</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.00220875273498</v>
+        <v>0.7670553005565959</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.002208649110752</v>
+        <v>0.767055196932368</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.002208529544335</v>
+        <v>0.7670550773659509</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.002208649110752</v>
+        <v>0.767055196932368</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.002208696937319</v>
+        <v>0.7670552447589347</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.002208792590452</v>
+        <v>0.7670553404120681</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.002208673024035</v>
+        <v>0.7670552208456514</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.00220868099513</v>
+        <v>0.7670552288167458</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000001.xlsx
+++ b/out/LSTM_Base_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02135039120912552</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01241689547896385</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007479004561901093</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.00543317012488842</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00345294363796711</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0007086340337991714</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.00245295837521553</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.002933451905846596</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001036949455738068</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001452483236789703</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0007313191890716553</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001032905653119087</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0007451139390468597</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.003871791064739227</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.005874373018741608</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005957670509815216</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002364616841077805</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.033277624339568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0007624905556440353</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.033277624339568</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0002501290291547775</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.244861115779144</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001099003478884697</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.2564446072187196</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001800891011953354</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001385267823934555</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0007441453635692596</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-5.19976019859314e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001342404633760452</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002198074012994766</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002410780638456345</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.002842336893081665</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001105021685361862</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4564446072187197</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001845737919211388</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0007232800126075745</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00150672160089016</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.003074659034609795</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3319719013417047</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.003073718398809433</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.002542387694120407</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0006263814866542816</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2564446072187198</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001262106001377106</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.244861115779144</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002954345196485519</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.033277624339568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.007446888834238052</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01075202971696854</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01611551269888878</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01830031350255013</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002660688213552349</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1145614023813524</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02348329126834869</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.033277624339568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2294287538274813</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4426121109477181</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0217263326048851</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.033277624339568</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.000384322575063</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1361494574716301</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003402071073651314</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.244861115779144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.829511836150113</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02762594425353835</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.007714357227087021</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2564446072187198</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7484002547363208</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02392529550028762</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01766267232596874</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7685943606303764</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01169618414811576</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01627875119447708</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7680312725147437</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005580246497245086</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01426331140100956</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7674815241808638</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002321491938506962</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01155396550893784</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7665384065563169</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001607793414154595</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01022196933627129</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7674298377112646</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006682799397292695</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005166197195649147</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.767156850961571</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003437855809979584</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003828532993793488</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.76717610937378</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001319895265635107</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00825110450387001</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7670957489439035</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.001495723500145e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.009529639035463333</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7671031110986752</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.170366259223818e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01098442077636719</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7670969839469558</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.258324531472877e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.009248550981283188</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7670898387334796</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.378749652309724e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.007256260141730309</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7670824528924171</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.00563289038836956</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7670766310869136</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004489615559577942</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7670707662909124</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004620891064405441</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7670650871142042</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002833593636751175</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7670602058159548</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003858894109725952</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.767055284614407</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001320557668805122</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7670552766433125</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001708842813968658</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7670554360652017</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.002005519345402718</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.244861115779144</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0003824569284915924</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.244861115779144</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7670556911402244</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003788987174630165</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7670554440362961</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004484428092837334</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3319719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7670554041808239</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.006489528343081474</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006408806890249252</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7670554121519183</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.00570298358798027</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2564446072187196</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.005899477750062943</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.244861115779144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7670554440362961</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.002468353137373924</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.244861115779144</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7670555396894299</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.005668548867106438</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7670554759206739</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00998581200838089</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7670554360652017</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.008342957124114037</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7670554121519183</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.008560875430703163</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7670551650479902</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.00834169052541256</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7670550853370454</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006162043660879135</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7670551331636121</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004914054647088051</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7670552527300292</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002670152112841606</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7670552367878403</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.00194866769015789</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7670552527300292</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0009694304317235947</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7670552367878403</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001154046505689621</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7670552925855014</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002667076885700226</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7670552925855014</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001402199268341064</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7670552925855014</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.000250697135925293</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7670554440362961</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.002986777573823929</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7670556592558466</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001599902287125587</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4564446072187197</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7670555715738077</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003455821424722672</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3319719013417047</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7670555237472408</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003643959760665894</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7670555715738077</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005369566380977631</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7670553882386349</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005594110116362572</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7670553962097294</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003619400784373283</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7670554041808239</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003828512504696846</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7670554121519183</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003376765176653862</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2564446072187196</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7670554121519183</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.000863153487443924</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.244861115779144</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7670554520073906</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001136865466833115</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.033277624339568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7670555157761464</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0008764192461967468</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7670556273714688</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002138674259185791</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7670556751980355</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002816133201122284</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7670556353425633</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002207186073064804</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7670555636027132</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002530671656131744</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.76705568316913</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003027407452464104</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7670555237472408</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006148574873805046</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7670552925855014</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006965577602386475</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7670552447589347</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.006928035989403725</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7670552766433125</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004616573452949524</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004672819748520851</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004484442993998528</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7670552607011236</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004054805263876915</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7670551411347065</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002989973872900009</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7670551012792343</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.000956609845161438</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7670552447589347</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0006550922989845276</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7670553802675405</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001964373514056206</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7670553643253516</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002223189920186996</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00240037776529789</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7670553005565959</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001882666721940041</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.767055196932368</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0003244262188673019</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7670550773659509</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002183280885219574</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.767055196932368</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001682043075561523</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7670552447589347</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002938251942396164</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7670553404120681</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003017459064722061</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7670552208456514</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001172192394733429</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7670552288167458</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_2_000001.xlsx
+++ b/out/LSTM_Base_repeat_2_000001.xlsx
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>-5.19976019859314e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>-0.001342404633760452</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>-0.002198074012994766</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>-0.002410780638456345</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>-0.002842336893081665</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>-0.003074659034609795</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>-0.003858894109725952</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
         <v>0.5237356632182673</v>
@@ -52619,7 +52619,7 @@
         <v>-0.001320557668805122</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
         <v>0.5237356552471728</v>
@@ -53414,7 +53414,7 @@
         <v>-0.001708842813968658</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0.5237358146690619</v>
@@ -54209,7 +54209,7 @@
         <v>0.002005519345402718</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0.5237357190159284</v>
@@ -55004,7 +55004,7 @@
         <v>0.0003824569284915924</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
         <v>0.5237360697440847</v>
@@ -56594,7 +56594,7 @@
         <v>-0.004484428092837334</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0.5237357827846841</v>
